--- a/Dataset/EN/xlsx/ITAMed_2019_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2019_EN.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Early gastric cancer is a lesion that is:</t>
+          <t>Early gastric cancer is a lesion that is</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>In the treatment of nociceptive pain without spinal sensitization, it is NOT indicated to administer:</t>
+          <t>In the treatment of nociceptive pain without spinal sensitization, it is NOT indicated to administer</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Spinal shock presents with:</t>
+          <t>Spinal shock presents with</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>When using a local anesthetic, it is NOT necessary to assess:</t>
+          <t>When using a local anesthetic, it is NOT necessary to assess</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A 15-year-old boy presents with asymmetry of the scrotum with painless swelling of the left hemiscrotum due to ectasia of the pampiniform plexus. The most appropriate diagnostic examination is:</t>
+          <t>A 15-year-old boy presents with asymmetry of the scrotum with painless swelling of the left hemiscrotum due to ectasia of the pampiniform plexus. The most appropriate diagnostic examination is</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A 50-year-old patient presents with a squamous cell carcinoma of the left lung, cT1, N1, M0. Surgery is planned to remove the neoplasm. The treatment of certain types of early-stage lung cancer involves surgical resection. Pneumonectomy:</t>
+          <t>A 50-year-old patient presents with a squamous cell carcinoma of the left lung, cT1, N1, M0. Surgery is planned to remove the neoplasm. The treatment of certain types of early-stage lung cancer involves surgical resection. Pneumonectomy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Merkel cells are mechanoreceptors:</t>
+          <t>Merkel cells are mechanoreceptors</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>The Barthel Index is used to assess:</t>
+          <t>The Barthel Index is used to assess</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Generally, during physiological pregnancy the functional residual capacity of the lungs:</t>
+          <t>Generally, during physiological pregnancy the functional residual capacity of the lungs</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The finding of high serum levels of CA 125:</t>
+          <t>The finding of high serum levels of CA 125</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>The gynecologist prescribes, for a woman in the 3rd month of pregnancy, testing for anti-Cytomegalovirus antibodies, which come back positive. In maternal Cytomegalovirus infection, the risk of fetal disease is:</t>
+          <t>The gynecologist prescribes, for a woman in the 3rd month of pregnancy, testing for anti-Cytomegalovirus antibodies, which come back positive. In maternal Cytomegalovirus infection, the risk of fetal disease is</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>The methacholine test refers to:</t>
+          <t>The methacholine test refers to</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wolff-Parkinson-White syndrome is characterized by:</t>
+          <t>Wolff-Parkinson-White syndrome is characterized by</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>A 55-year-old man, a worker in a textile factory, complains of recurrent low back pain that he attributes to his job duties, which involve repeated lifting of heavy loads. Manual handling of loads is regulated by Annex XXXIII of Legislative Decree 81/2008, which provides for the application of the models indicated by the UNI ISO 11228 standard. According to this annex, the maximum weight that can be lifted by a male subject over forty-five years of age is equal to:</t>
+          <t>A 55-year-old man, a worker in a textile factory, complains of recurrent low back pain that he attributes to his job duties, which involve repeated lifting of heavy loads. Manual handling of loads is regulated by Annex XXXIII of Legislative Decree 81/2008, which provides for the application of the models indicated by the UNI ISO 11228 standard. According to this annex, the maximum weight that can be lifted by a male subject over forty-five years of age is equal to</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>A 22-year-old woman presents to the gynecological Emergency Department and reports that during a private party she was approached by an unknown man who then sexually assaulted her. The on-call gynecologist must:</t>
+          <t>A 22-year-old woman presents to the gynecological Emergency Department and reports that during a private party she was approached by an unknown man who then sexually assaulted her. The on-call gynecologist must</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>A boy, returning from school, while crossing the street at a pedestrian crossing, is struck by a car in the act of overtaking. He is first thrown onto the hood of the car and then propelled several meters away, sustaining polytrauma. After being attended to by the 118 emergency medical service and undergoing instrumental investigations, he is admitted to the hospital's Orthopedics ward with a diagnosis of "open fracture of the right radius, displaced fracture of the left radius, and displaced fracture of both bones of the left leg." In light of the severity of the injuries found, the Emergency Department physician must:</t>
+          <t>A boy, returning from school, while crossing the street at a pedestrian crossing, is struck by a car in the act of overtaking. He is first thrown onto the hood of the car and then propelled several meters away, sustaining polytrauma. After being attended to by the 118 emergency medical service and undergoing instrumental investigations, he is admitted to the hospital's Orthopedics ward with a diagnosis of "open fracture of the right radius, displaced fracture of the left radius, and displaced fracture of both bones of the left leg." In light of the severity of the injuries found, the Emergency Department physician must</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>A 7-year-old boy presents to an ophthalmologist's office accompanied by his parents, who report that over the past few months their son has been getting very close to objects to observe them. The child, who is particularly tall for his age, has compound myopic astigmatism -4.00 sph -2.00 cyl 100° in one eye and ectopia lentis in the other. Based on the clinical picture described, it is correct to suspect:</t>
+          <t>A 7-year-old boy presents to an ophthalmologist's office accompanied by his parents, who report that over the past few months their son has been getting very close to objects to observe them. The child, who is particularly tall for his age, has compound myopic astigmatism -4.00 sph -2.00 cyl 100° in one eye and ectopia lentis in the other. Based on the clinical picture described, it is correct to suspect</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Legg-Calvé-Perthes disease refers to:</t>
+          <t>Legg-Calvé-Perthes disease refers to</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Monteggia fracture-dislocation is characterized by:</t>
+          <t>Monteggia fracture-dislocation is characterized by</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>A 65-year-old man presents to the outpatient clinic complaining of progressive and disabling flexion stiffness of the 4th and 5th fingers of the right hand. On physical examination, this flexion posture is not reducible and is accompanied by the presence of a raised, sclerotic, cord-like thickening at the palmar level, corresponding to the 4th and 5th fingers. From this clinical picture, a diagnosis can be made of:</t>
+          <t>A 65-year-old man presents to the outpatient clinic complaining of progressive and disabling flexion stiffness of the 4th and 5th fingers of the right hand. On physical examination, this flexion posture is not reducible and is accompanied by the presence of a raised, sclerotic, cord-like thickening at the palmar level, corresponding to the 4th and 5th fingers. From this clinical picture, a diagnosis can be made of</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Activation of the extrinsic pathway of coagulation can be triggered by vascular injury, as this event leads to the release of:</t>
+          <t>Activation of the extrinsic pathway of coagulation can be triggered by vascular injury, as this event leads to the release of</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>In tetralogy of Fallot, the severity of arterial hypoxemia generally depends mainly on:</t>
+          <t>In tetralogy of Fallot, the severity of arterial hypoxemia generally depends mainly on</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2019_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2019_EN.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Immunology and Rheumatology; Anesthesia and Intensive Care</t>
+          <t>Immunology and Rheumatology</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Forensic Medicine</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Anesthesia and Intensive Care</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Anesthesia and Intensive Care</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; General Surgery</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>General Surgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Oncology; Gastroenterology</t>
+          <t>Gastroenterology; Oncology</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; General Surgery</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Endocrinology; Pharmacology and Toxicology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Medical Genetics</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Pulmonology and Thoracic Surgery</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Hematology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Gastroenterology; Hematology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery</t>
+          <t>Infectious Diseases; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Hematology; Gynecology and Obstetrics</t>
+          <t>Gynecology and Obstetrics; Hematology</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Infectious Diseases</t>
+          <t>Infectious Diseases; Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Pediatrics; Psychiatry</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Oncology; Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Pediatrics</t>
+          <t>Pediatrics; Otorhinolaryngology</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Pediatrics</t>
+          <t>Pediatrics; Otorhinolaryngology</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pediatrics</t>
+          <t>Pediatrics; Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Medical Genetics; Pediatrics</t>
+          <t>Pediatrics; Medical Genetics</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Nephrology; Pediatrics</t>
+          <t>Pediatrics; Nephrology</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Hematology; Pediatrics</t>
+          <t>Medical Genetics</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Endocrinology; Pediatrics</t>
+          <t>Pediatrics; Endocrinology</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Hygiene, Epidemiology and Statistics</t>
+          <t>Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2019_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2019_EN.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/EN/xlsx/ITAMed_2019_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2019_EN.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -473,15 +473,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Image Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Image Path</t>
         </is>
@@ -544,6 +549,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -602,6 +612,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -660,6 +675,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -718,6 +738,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -776,6 +801,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -834,6 +864,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -892,6 +927,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -950,6 +990,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1008,6 +1053,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1066,6 +1116,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1124,6 +1179,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1182,6 +1242,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1240,6 +1305,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1298,6 +1368,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1356,6 +1431,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1414,6 +1494,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1472,6 +1557,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1530,6 +1620,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1588,6 +1683,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1646,6 +1746,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1704,6 +1809,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1762,6 +1872,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1820,6 +1935,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1878,6 +1998,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1936,6 +2061,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1994,6 +2124,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2052,6 +2187,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2110,6 +2250,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2168,6 +2313,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2226,6 +2376,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2286,10 +2441,15 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>images/2019/ssm201960.png</t>
         </is>
@@ -2352,6 +2512,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2410,6 +2575,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2468,6 +2638,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2526,6 +2701,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2584,6 +2764,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2642,6 +2827,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2700,6 +2890,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2758,6 +2953,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2816,6 +3016,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2874,6 +3079,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2932,6 +3142,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2990,6 +3205,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3048,6 +3268,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3106,6 +3331,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3164,6 +3394,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3222,6 +3457,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3280,6 +3520,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3338,6 +3583,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3396,6 +3646,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3454,6 +3709,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3512,6 +3772,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3570,6 +3835,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3628,6 +3898,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3686,6 +3961,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3744,6 +4024,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3802,6 +4087,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3860,6 +4150,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3918,6 +4213,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3978,10 +4278,15 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>Chest X-ray</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>images/2019/ssm2019119.png</t>
         </is>
@@ -4044,6 +4349,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4102,6 +4412,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4160,6 +4475,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4218,6 +4538,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4276,6 +4601,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4334,6 +4664,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4392,6 +4727,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4450,6 +4790,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4508,6 +4853,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4566,6 +4916,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4624,6 +4979,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4682,6 +5042,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4740,6 +5105,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4798,6 +5168,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4856,6 +5231,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4914,6 +5294,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4972,6 +5357,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5030,6 +5420,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5088,6 +5483,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5146,6 +5546,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5204,6 +5609,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5262,6 +5672,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5320,6 +5735,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5378,6 +5798,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5436,6 +5861,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5494,6 +5924,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5552,6 +5987,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5610,6 +6050,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5668,6 +6113,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5726,6 +6176,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5784,6 +6239,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5842,6 +6302,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5900,6 +6365,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5958,6 +6428,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6018,10 +6493,15 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>images/2019/ssm2019189.png</t>
         </is>
@@ -6084,6 +6564,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6142,6 +6627,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6200,6 +6690,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6258,6 +6753,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6316,6 +6816,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6374,6 +6879,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6432,6 +6942,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6490,6 +7005,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6548,6 +7068,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6606,6 +7131,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6664,6 +7194,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6722,6 +7257,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6780,6 +7320,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6838,6 +7383,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6898,10 +7448,15 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
           <t>Upper limb X-ray</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>images/2019/ssm2019216.png</t>
         </is>
@@ -6964,6 +7519,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7022,6 +7582,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7080,6 +7645,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7138,6 +7708,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7196,6 +7771,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7254,6 +7834,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7312,6 +7897,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7370,6 +7960,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7428,6 +8023,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7486,6 +8086,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7541,7 +8146,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7602,6 +8212,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7660,6 +8275,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7718,6 +8338,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7773,7 +8398,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7834,6 +8464,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7892,6 +8527,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7952,10 +8592,15 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr">
+      <c r="O129" t="inlineStr">
         <is>
           <t>images/2019/ssm2019254.png</t>
         </is>
@@ -8018,6 +8663,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8076,6 +8726,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8134,6 +8789,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8192,6 +8852,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8250,6 +8915,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8308,6 +8978,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8366,6 +9041,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8424,6 +9104,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8482,6 +9167,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8540,6 +9230,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8598,6 +9293,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8654,6 +9354,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>case-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
